--- a/data_judul_ta_MI.xlsx
+++ b/data_judul_ta_MI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TA\SIMTA-FASILKOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2F033B-F93A-47AD-A1FD-D5013A8C5F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09C8675-77A2-44BA-B9AD-F2DD69FE76AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7255,7 +7255,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I389"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7298,7 +7297,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -7328,7 +7327,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -7358,7 +7357,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -7388,7 +7387,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -7418,7 +7417,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -7448,7 +7447,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -7478,7 +7477,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -7508,7 +7507,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -7538,7 +7537,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -7568,7 +7567,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -7598,7 +7597,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -7628,7 +7627,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -7658,7 +7657,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -7688,7 +7687,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -7718,7 +7717,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -7748,7 +7747,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -7778,7 +7777,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -7808,7 +7807,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -7838,7 +7837,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -7868,7 +7867,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -7898,7 +7897,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -7928,7 +7927,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -7958,7 +7957,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -7988,7 +7987,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -8018,7 +8017,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -8048,7 +8047,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -8078,7 +8077,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -8108,7 +8107,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>28</v>
       </c>
@@ -8138,7 +8137,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -8168,7 +8167,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>30</v>
       </c>
@@ -8198,7 +8197,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -8228,7 +8227,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -8258,7 +8257,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -8288,7 +8287,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -8318,7 +8317,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -8348,7 +8347,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>36</v>
       </c>
@@ -8378,7 +8377,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -8408,7 +8407,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>38</v>
       </c>
@@ -8438,7 +8437,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -8468,7 +8467,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>40</v>
       </c>
@@ -8498,7 +8497,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -8528,7 +8527,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>42</v>
       </c>
@@ -8558,7 +8557,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -8588,7 +8587,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>44</v>
       </c>
@@ -8618,7 +8617,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -8648,7 +8647,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>46</v>
       </c>
@@ -8678,7 +8677,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -8708,7 +8707,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>48</v>
       </c>
@@ -8738,7 +8737,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -8768,7 +8767,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>50</v>
       </c>
@@ -8798,7 +8797,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -8828,7 +8827,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>52</v>
       </c>
@@ -8858,7 +8857,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -8888,7 +8887,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>54</v>
       </c>
@@ -8918,7 +8917,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -8948,7 +8947,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>56</v>
       </c>
@@ -8978,7 +8977,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -9008,7 +9007,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>58</v>
       </c>
@@ -9038,7 +9037,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -9068,7 +9067,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>60</v>
       </c>
@@ -9098,7 +9097,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -9128,7 +9127,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>62</v>
       </c>
@@ -9158,7 +9157,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -9188,7 +9187,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>64</v>
       </c>
@@ -9218,7 +9217,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -9248,7 +9247,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>66</v>
       </c>
@@ -9278,7 +9277,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -9308,7 +9307,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6">
         <v>68</v>
       </c>
@@ -9338,7 +9337,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -9368,7 +9367,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="6">
         <v>70</v>
       </c>
@@ -9398,7 +9397,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -9428,7 +9427,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="6">
         <v>72</v>
       </c>
@@ -9458,7 +9457,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -9488,7 +9487,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="6">
         <v>74</v>
       </c>
@@ -9518,7 +9517,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -9548,7 +9547,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="6">
         <v>76</v>
       </c>
@@ -9578,7 +9577,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -9608,7 +9607,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="6">
         <v>78</v>
       </c>
@@ -9638,7 +9637,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -9668,7 +9667,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>80</v>
       </c>
@@ -9698,7 +9697,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -9728,7 +9727,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="6">
         <v>82</v>
       </c>
@@ -9758,7 +9757,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -9788,7 +9787,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>84</v>
       </c>
@@ -9818,7 +9817,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -9848,7 +9847,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6">
         <v>86</v>
       </c>
@@ -9878,7 +9877,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -9908,7 +9907,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="6">
         <v>88</v>
       </c>
@@ -9938,7 +9937,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -9968,7 +9967,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="6">
         <v>90</v>
       </c>
@@ -9998,7 +9997,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -10028,7 +10027,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="6">
         <v>92</v>
       </c>
@@ -10058,7 +10057,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -10088,7 +10087,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="6">
         <v>94</v>
       </c>
@@ -10118,7 +10117,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -10148,7 +10147,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="6">
         <v>96</v>
       </c>
@@ -10178,7 +10177,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -10208,7 +10207,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="6">
         <v>98</v>
       </c>
@@ -10238,7 +10237,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -10268,7 +10267,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="6">
         <v>100</v>
       </c>
@@ -10298,7 +10297,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -10328,7 +10327,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="6">
         <v>102</v>
       </c>
@@ -10358,7 +10357,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -10388,7 +10387,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="6">
         <v>104</v>
       </c>
@@ -10418,7 +10417,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -10448,7 +10447,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="6">
         <v>106</v>
       </c>
@@ -10478,7 +10477,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -10508,7 +10507,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="6">
         <v>108</v>
       </c>
@@ -10538,7 +10537,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -10568,7 +10567,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="6">
         <v>110</v>
       </c>
@@ -10598,7 +10597,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -10628,7 +10627,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="6">
         <v>112</v>
       </c>
@@ -10658,7 +10657,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -10688,7 +10687,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="6">
         <v>114</v>
       </c>
@@ -10718,7 +10717,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -10748,7 +10747,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="6">
         <v>116</v>
       </c>
@@ -10778,7 +10777,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -10808,7 +10807,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="6">
         <v>118</v>
       </c>
@@ -10838,7 +10837,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -10868,7 +10867,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="6">
         <v>120</v>
       </c>
@@ -10898,7 +10897,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -10928,7 +10927,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="6">
         <v>122</v>
       </c>
@@ -10958,7 +10957,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -10988,7 +10987,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="6">
         <v>124</v>
       </c>
@@ -11018,7 +11017,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -11048,7 +11047,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="6">
         <v>126</v>
       </c>
@@ -11078,7 +11077,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -11108,7 +11107,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="6">
         <v>128</v>
       </c>
@@ -11138,7 +11137,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -11168,7 +11167,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="6">
         <v>130</v>
       </c>
@@ -11198,7 +11197,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -11228,7 +11227,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="6">
         <v>132</v>
       </c>
@@ -11258,7 +11257,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -11288,7 +11287,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="6">
         <v>134</v>
       </c>
@@ -11318,7 +11317,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>135</v>
       </c>
@@ -11348,7 +11347,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="6">
         <v>136</v>
       </c>
@@ -11378,7 +11377,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -11408,7 +11407,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="6">
         <v>138</v>
       </c>
@@ -11438,7 +11437,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -11468,7 +11467,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="6">
         <v>140</v>
       </c>
@@ -11498,7 +11497,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -11528,7 +11527,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="6">
         <v>142</v>
       </c>
@@ -11558,7 +11557,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>143</v>
       </c>
@@ -11588,7 +11587,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="6">
         <v>144</v>
       </c>
@@ -11618,7 +11617,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -11648,7 +11647,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="6">
         <v>146</v>
       </c>
@@ -11678,7 +11677,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -11708,7 +11707,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="6">
         <v>148</v>
       </c>
@@ -11738,7 +11737,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -11768,7 +11767,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="6">
         <v>150</v>
       </c>
@@ -11798,7 +11797,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -11828,7 +11827,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="6">
         <v>152</v>
       </c>
@@ -11858,7 +11857,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -11888,7 +11887,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="6">
         <v>154</v>
       </c>
@@ -11918,7 +11917,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -11948,7 +11947,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="6">
         <v>156</v>
       </c>
@@ -11978,7 +11977,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -12008,7 +12007,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="6">
         <v>158</v>
       </c>
@@ -12038,7 +12037,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -12068,7 +12067,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="6">
         <v>160</v>
       </c>
@@ -12098,7 +12097,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>161</v>
       </c>
@@ -12128,7 +12127,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="6">
         <v>162</v>
       </c>
@@ -12158,7 +12157,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -12188,7 +12187,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="6">
         <v>164</v>
       </c>
@@ -12218,7 +12217,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>165</v>
       </c>
@@ -12248,7 +12247,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="6">
         <v>166</v>
       </c>
@@ -12278,7 +12277,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>167</v>
       </c>
@@ -12308,7 +12307,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="6">
         <v>168</v>
       </c>
@@ -12338,7 +12337,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>169</v>
       </c>
@@ -12368,7 +12367,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="6">
         <v>170</v>
       </c>
@@ -12398,7 +12397,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -12428,7 +12427,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="6">
         <v>172</v>
       </c>
@@ -12458,7 +12457,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>173</v>
       </c>
@@ -12488,7 +12487,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="6">
         <v>174</v>
       </c>
@@ -12518,7 +12517,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -12548,7 +12547,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="6">
         <v>176</v>
       </c>
@@ -12578,7 +12577,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>177</v>
       </c>
@@ -12608,7 +12607,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="6">
         <v>178</v>
       </c>
@@ -12638,7 +12637,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>179</v>
       </c>
@@ -12668,7 +12667,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="6">
         <v>180</v>
       </c>
@@ -12698,7 +12697,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>181</v>
       </c>
@@ -12728,7 +12727,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="6">
         <v>182</v>
       </c>
@@ -12758,7 +12757,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>183</v>
       </c>
@@ -12788,7 +12787,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="6">
         <v>184</v>
       </c>
@@ -12818,7 +12817,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>185</v>
       </c>
@@ -12848,7 +12847,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="6">
         <v>186</v>
       </c>
@@ -12878,7 +12877,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>187</v>
       </c>
@@ -12908,7 +12907,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="6">
         <v>188</v>
       </c>
@@ -12938,7 +12937,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>189</v>
       </c>
@@ -12968,7 +12967,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="6">
         <v>190</v>
       </c>
@@ -12998,7 +12997,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>191</v>
       </c>
@@ -13028,7 +13027,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="6">
         <v>192</v>
       </c>
@@ -13058,7 +13057,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>193</v>
       </c>
@@ -13088,7 +13087,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="6">
         <v>194</v>
       </c>
@@ -13118,7 +13117,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>195</v>
       </c>
@@ -13148,7 +13147,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="6">
         <v>196</v>
       </c>
@@ -13178,7 +13177,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>197</v>
       </c>
@@ -13208,7 +13207,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="6">
         <v>198</v>
       </c>
@@ -13238,7 +13237,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>199</v>
       </c>
@@ -13268,7 +13267,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="6">
         <v>200</v>
       </c>
@@ -13298,7 +13297,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>201</v>
       </c>
@@ -13328,7 +13327,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="6">
         <v>202</v>
       </c>
@@ -13358,7 +13357,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>203</v>
       </c>
@@ -13388,7 +13387,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="6">
         <v>204</v>
       </c>
@@ -13418,7 +13417,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>205</v>
       </c>
@@ -13448,7 +13447,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="6">
         <v>206</v>
       </c>
@@ -13478,7 +13477,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>207</v>
       </c>
@@ -13508,7 +13507,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="6">
         <v>208</v>
       </c>
@@ -13538,7 +13537,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>209</v>
       </c>
@@ -13568,7 +13567,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="6">
         <v>210</v>
       </c>
@@ -13598,7 +13597,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>211</v>
       </c>
@@ -13628,7 +13627,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="6">
         <v>212</v>
       </c>
@@ -13658,7 +13657,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>213</v>
       </c>
@@ -13688,7 +13687,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="6">
         <v>214</v>
       </c>
@@ -13718,7 +13717,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>215</v>
       </c>
@@ -13748,7 +13747,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="6">
         <v>216</v>
       </c>
@@ -13778,7 +13777,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>217</v>
       </c>
@@ -13808,7 +13807,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="6">
         <v>218</v>
       </c>
@@ -13838,7 +13837,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>219</v>
       </c>
@@ -13868,7 +13867,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="6">
         <v>220</v>
       </c>
@@ -13898,7 +13897,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>221</v>
       </c>
@@ -13928,7 +13927,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="6">
         <v>222</v>
       </c>
@@ -13958,7 +13957,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>223</v>
       </c>
@@ -13988,7 +13987,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="6">
         <v>224</v>
       </c>
@@ -14018,7 +14017,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>225</v>
       </c>
@@ -14048,7 +14047,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="6">
         <v>226</v>
       </c>
@@ -14078,7 +14077,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>227</v>
       </c>
@@ -14108,7 +14107,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="6">
         <v>228</v>
       </c>
@@ -14138,7 +14137,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>229</v>
       </c>
@@ -14168,7 +14167,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="6">
         <v>230</v>
       </c>
@@ -14198,7 +14197,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>231</v>
       </c>
@@ -14228,7 +14227,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="6">
         <v>232</v>
       </c>
@@ -14258,7 +14257,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>233</v>
       </c>
@@ -14288,7 +14287,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="6">
         <v>234</v>
       </c>
@@ -14318,7 +14317,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>235</v>
       </c>
@@ -14348,7 +14347,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="6">
         <v>236</v>
       </c>
@@ -14378,7 +14377,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>237</v>
       </c>
@@ -14408,7 +14407,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="6">
         <v>238</v>
       </c>
@@ -14438,7 +14437,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>239</v>
       </c>
@@ -14468,7 +14467,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="6">
         <v>240</v>
       </c>
@@ -14498,7 +14497,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>241</v>
       </c>
@@ -14528,7 +14527,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="6">
         <v>242</v>
       </c>
@@ -14558,7 +14557,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>243</v>
       </c>
@@ -14588,7 +14587,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="6">
         <v>244</v>
       </c>
@@ -14618,7 +14617,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="2">
         <v>245</v>
       </c>
@@ -14648,7 +14647,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="6">
         <v>246</v>
       </c>
@@ -14678,7 +14677,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="2">
         <v>247</v>
       </c>
@@ -14708,7 +14707,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="6">
         <v>248</v>
       </c>
@@ -14738,7 +14737,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="2">
         <v>249</v>
       </c>
@@ -14768,7 +14767,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="6">
         <v>250</v>
       </c>
@@ -14798,7 +14797,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2">
         <v>251</v>
       </c>
@@ -14828,7 +14827,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="6">
         <v>252</v>
       </c>
@@ -14858,7 +14857,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="2">
         <v>253</v>
       </c>
@@ -14888,7 +14887,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="6">
         <v>254</v>
       </c>
@@ -14918,7 +14917,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="2">
         <v>255</v>
       </c>
@@ -14948,7 +14947,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="6">
         <v>256</v>
       </c>
@@ -14978,7 +14977,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="2">
         <v>257</v>
       </c>
@@ -15008,7 +15007,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="6">
         <v>258</v>
       </c>
@@ -15038,7 +15037,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="2">
         <v>259</v>
       </c>
@@ -15068,7 +15067,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="6">
         <v>260</v>
       </c>
@@ -15098,7 +15097,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2">
         <v>261</v>
       </c>
@@ -15128,7 +15127,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="6">
         <v>262</v>
       </c>
@@ -15158,7 +15157,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2">
         <v>263</v>
       </c>
@@ -15188,7 +15187,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="6">
         <v>264</v>
       </c>
@@ -15218,7 +15217,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="2">
         <v>265</v>
       </c>
@@ -15248,7 +15247,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="6">
         <v>266</v>
       </c>
@@ -15278,7 +15277,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="2">
         <v>267</v>
       </c>
@@ -15308,7 +15307,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="6">
         <v>268</v>
       </c>
@@ -15338,7 +15337,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="2">
         <v>269</v>
       </c>
@@ -15368,7 +15367,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="6">
         <v>270</v>
       </c>
@@ -15398,7 +15397,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="2">
         <v>271</v>
       </c>
@@ -15428,7 +15427,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="6">
         <v>272</v>
       </c>
@@ -15458,7 +15457,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="2">
         <v>273</v>
       </c>
@@ -15488,7 +15487,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="6">
         <v>274</v>
       </c>
@@ -15518,7 +15517,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="2">
         <v>275</v>
       </c>
@@ -15548,7 +15547,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="6">
         <v>276</v>
       </c>
@@ -15578,7 +15577,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="2">
         <v>277</v>
       </c>
@@ -15608,7 +15607,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="6">
         <v>278</v>
       </c>
@@ -15638,7 +15637,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="2">
         <v>279</v>
       </c>
@@ -15668,7 +15667,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="6">
         <v>280</v>
       </c>
@@ -15698,7 +15697,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="2">
         <v>281</v>
       </c>
@@ -15728,7 +15727,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="6">
         <v>282</v>
       </c>
@@ -15758,7 +15757,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="2">
         <v>283</v>
       </c>
@@ -15788,7 +15787,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="6">
         <v>284</v>
       </c>
@@ -15818,7 +15817,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="2">
         <v>285</v>
       </c>
@@ -15848,7 +15847,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="6">
         <v>286</v>
       </c>
@@ -15878,7 +15877,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="2">
         <v>287</v>
       </c>
@@ -15908,7 +15907,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="6">
         <v>288</v>
       </c>
@@ -15938,7 +15937,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="2">
         <v>289</v>
       </c>
@@ -15968,7 +15967,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="6">
         <v>290</v>
       </c>
@@ -15998,7 +15997,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="2">
         <v>291</v>
       </c>
@@ -16028,7 +16027,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="6">
         <v>292</v>
       </c>
@@ -16058,7 +16057,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2">
         <v>293</v>
       </c>
@@ -16088,7 +16087,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="6">
         <v>294</v>
       </c>
@@ -16118,7 +16117,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="2">
         <v>295</v>
       </c>
@@ -16148,7 +16147,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="6">
         <v>296</v>
       </c>
@@ -16178,7 +16177,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="2">
         <v>297</v>
       </c>
@@ -16208,7 +16207,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="6">
         <v>298</v>
       </c>
@@ -16238,7 +16237,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="2">
         <v>299</v>
       </c>
@@ -16268,7 +16267,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="6">
         <v>300</v>
       </c>
@@ -16298,7 +16297,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="2">
         <v>301</v>
       </c>
@@ -16328,7 +16327,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="6">
         <v>302</v>
       </c>
@@ -16358,7 +16357,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="2">
         <v>303</v>
       </c>
@@ -16388,7 +16387,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="6">
         <v>304</v>
       </c>
@@ -16418,7 +16417,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2">
         <v>305</v>
       </c>
@@ -16448,7 +16447,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="6">
         <v>306</v>
       </c>
@@ -16478,7 +16477,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="2">
         <v>307</v>
       </c>
@@ -16508,7 +16507,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="6">
         <v>308</v>
       </c>
@@ -16538,7 +16537,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="2">
         <v>309</v>
       </c>
@@ -16568,7 +16567,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="6">
         <v>310</v>
       </c>
@@ -16598,7 +16597,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="2">
         <v>311</v>
       </c>
@@ -16628,7 +16627,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="6">
         <v>312</v>
       </c>
@@ -16658,7 +16657,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="2">
         <v>313</v>
       </c>
@@ -16688,7 +16687,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="6">
         <v>314</v>
       </c>
@@ -16718,7 +16717,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="2">
         <v>315</v>
       </c>
@@ -16748,7 +16747,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="6">
         <v>316</v>
       </c>
@@ -16778,7 +16777,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="2">
         <v>317</v>
       </c>
@@ -16808,7 +16807,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="6">
         <v>318</v>
       </c>
@@ -16838,7 +16837,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="2">
         <v>319</v>
       </c>
@@ -16868,7 +16867,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="6">
         <v>320</v>
       </c>
@@ -16898,7 +16897,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2">
         <v>321</v>
       </c>
@@ -16928,7 +16927,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="6">
         <v>322</v>
       </c>
@@ -16958,7 +16957,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="2">
         <v>323</v>
       </c>
@@ -16988,7 +16987,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="6">
         <v>324</v>
       </c>
@@ -17018,7 +17017,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="2">
         <v>325</v>
       </c>
@@ -17048,7 +17047,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="6">
         <v>326</v>
       </c>
@@ -17078,7 +17077,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="2">
         <v>327</v>
       </c>
@@ -17108,7 +17107,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="329" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="6">
         <v>328</v>
       </c>
@@ -17138,7 +17137,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="2">
         <v>329</v>
       </c>
@@ -17168,7 +17167,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="6">
         <v>330</v>
       </c>
@@ -17198,7 +17197,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2">
         <v>331</v>
       </c>
@@ -17228,7 +17227,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="6">
         <v>332</v>
       </c>
@@ -17258,7 +17257,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="2">
         <v>333</v>
       </c>
@@ -17288,7 +17287,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="6">
         <v>334</v>
       </c>
@@ -17318,7 +17317,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="2">
         <v>335</v>
       </c>
@@ -17348,7 +17347,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="6">
         <v>336</v>
       </c>
@@ -17378,7 +17377,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2">
         <v>337</v>
       </c>
@@ -17408,7 +17407,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="6">
         <v>338</v>
       </c>
@@ -17438,7 +17437,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2">
         <v>339</v>
       </c>
@@ -17468,7 +17467,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="6">
         <v>340</v>
       </c>
@@ -17498,7 +17497,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2">
         <v>341</v>
       </c>
@@ -17528,7 +17527,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="6">
         <v>342</v>
       </c>
@@ -17558,7 +17557,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="2">
         <v>343</v>
       </c>
@@ -17588,7 +17587,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="6">
         <v>344</v>
       </c>
@@ -17618,7 +17617,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="2">
         <v>345</v>
       </c>
@@ -17648,7 +17647,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="6">
         <v>346</v>
       </c>
@@ -17678,7 +17677,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="2">
         <v>347</v>
       </c>
@@ -17708,7 +17707,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="6">
         <v>348</v>
       </c>
@@ -17738,7 +17737,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2">
         <v>349</v>
       </c>
@@ -17768,7 +17767,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="6">
         <v>350</v>
       </c>
@@ -17798,7 +17797,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="2">
         <v>351</v>
       </c>
@@ -17828,7 +17827,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="6">
         <v>352</v>
       </c>
@@ -17858,7 +17857,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="2">
         <v>353</v>
       </c>
@@ -17888,7 +17887,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="6">
         <v>354</v>
       </c>
@@ -17918,7 +17917,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="2">
         <v>355</v>
       </c>
@@ -17948,7 +17947,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="6">
         <v>356</v>
       </c>
@@ -17978,7 +17977,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="2">
         <v>357</v>
       </c>
@@ -18008,7 +18007,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="6">
         <v>358</v>
       </c>
@@ -18038,7 +18037,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="2">
         <v>359</v>
       </c>
@@ -18068,7 +18067,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="6">
         <v>360</v>
       </c>
@@ -18098,7 +18097,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="2">
         <v>361</v>
       </c>
@@ -18128,7 +18127,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="6">
         <v>362</v>
       </c>
@@ -18158,7 +18157,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="2">
         <v>363</v>
       </c>
@@ -18188,7 +18187,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="6">
         <v>364</v>
       </c>
@@ -18218,7 +18217,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="2">
         <v>365</v>
       </c>
@@ -18248,7 +18247,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="6">
         <v>366</v>
       </c>
@@ -18278,7 +18277,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="2">
         <v>367</v>
       </c>
@@ -18308,7 +18307,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="6">
         <v>368</v>
       </c>
@@ -18338,7 +18337,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="2">
         <v>369</v>
       </c>
@@ -18368,7 +18367,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="6">
         <v>370</v>
       </c>
@@ -18398,7 +18397,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="2">
         <v>371</v>
       </c>
@@ -18428,7 +18427,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="6">
         <v>372</v>
       </c>
@@ -18458,7 +18457,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="2">
         <v>373</v>
       </c>
@@ -18488,7 +18487,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="6">
         <v>374</v>
       </c>
@@ -18518,7 +18517,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="2">
         <v>375</v>
       </c>
@@ -18548,7 +18547,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="6">
         <v>376</v>
       </c>
@@ -18578,7 +18577,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="2">
         <v>377</v>
       </c>
@@ -18608,7 +18607,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="6">
         <v>378</v>
       </c>
@@ -18638,7 +18637,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="2">
         <v>379</v>
       </c>
@@ -18668,7 +18667,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="6">
         <v>380</v>
       </c>
@@ -18698,7 +18697,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="2">
         <v>381</v>
       </c>
@@ -18758,7 +18757,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="2">
         <v>383</v>
       </c>
@@ -18788,7 +18787,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="6">
         <v>384</v>
       </c>
@@ -18818,7 +18817,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="2">
         <v>385</v>
       </c>
@@ -18848,7 +18847,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="6">
         <v>386</v>
       </c>
@@ -18878,7 +18877,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="2">
         <v>387</v>
       </c>
@@ -18908,7 +18907,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:9" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="6">
         <v>388</v>
       </c>
@@ -18939,13 +18938,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I389" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="2013"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I389" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
